--- a/aprēķini.xlsx
+++ b/aprēķini.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d25c33ae9209fa2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d25c33ae9209fa2/Dators/jakabs_gulbs/HTML5Application1/public_html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B587F09-D391-45D5-BED1-08F1D9944F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{9B587F09-D391-45D5-BED1-08F1D9944F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C65AD62-EEFD-446F-B9C8-8134472E225A}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22276" windowHeight="13996" xr2:uid="{E4B3F6C6-DC53-4207-AE48-00A7CA53D434}"/>
+    <workbookView xWindow="2115" yWindow="2115" windowWidth="16560" windowHeight="9533" xr2:uid="{E4B3F6C6-DC53-4207-AE48-00A7CA53D434}"/>
   </bookViews>
   <sheets>
     <sheet name="Reni" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="14">
   <si>
     <t>2. leņķis</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>rel kluda</t>
+  </si>
+  <si>
+    <t>m</t>
   </si>
 </sst>
 </file>
@@ -446,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03C39BFD-2D24-40A8-A419-368400D0B1D1}">
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
@@ -887,6 +890,11 @@
         <v>2.1358841953745294E-2</v>
       </c>
     </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="J12" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
